--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD_DP/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.66 ± 0.06</t>
+          <t>0.65 ± 0.06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.61 ± 0.04</t>
+          <t>0.58 ± 0.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73 ± 0.17</t>
+          <t>0.52 ± 0.18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.16</t>
+          <t>0.71 ± 0.19</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.69 ± 0.15</t>
+          <t>0.66 ± 0.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,12 +528,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.78 ± 0.14</t>
+          <t>0.76 ± 0.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F4" t="n">
